--- a/Details_WBS.xlsx
+++ b/Details_WBS.xlsx
@@ -1201,7 +1201,7 @@
       </c>
       <c r="F2" s="37" t="n"/>
       <c r="G2" s="29" t="n">
-        <v>45670</v>
+        <v>45671</v>
       </c>
       <c r="H2" s="37" t="n"/>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>01/13/2025</t>
+          <t>01/14/2025</t>
         </is>
       </c>
       <c r="D6" s="26" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaharuddin, Jannatil Anwar Bin </t>
+          <t xml:space="preserve">Nuramira Binti Ahmad Mahmud </t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>01/13/2025</t>
+          <t>01/14/2025</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>01/17/2025</t>
+          <t>01/28/2025</t>
         </is>
       </c>
       <c r="G9" s="3" t="n"/>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaharuddin, Jannatil Anwar Bin </t>
+          <t xml:space="preserve">Nuramira Binti Ahmad Mahmud </t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>01/20/2025</t>
+          <t>01/29/2025</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>01/24/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="G10" s="3" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaharuddin, Jannatil Anwar Bin </t>
+          <t xml:space="preserve">Nur Ain Binti Mahamad Salleh </t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>01/27/2025</t>
+          <t>01/14/2025</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>01/31/2025</t>
+          <t>01/28/2025</t>
         </is>
       </c>
       <c r="G11" s="3" t="n"/>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WBS001PRO001_CreateLoginFunction </t>
+          <t xml:space="preserve">WBS004_UI </t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaharuddin, Jannatil Anwar Bin </t>
+          <t xml:space="preserve">Nur Ain Binti Mahamad Salleh </t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>01/13/2025</t>
+          <t>01/29/2025</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>01/27/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="G12" s="3" t="n"/>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WBS001PRO003_CreateRegisterFunction </t>
+          <t xml:space="preserve">WBS001PRO001_CreateLoginFunction </t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaharuddin, Jannatil Anwar Bin </t>
+          <t xml:space="preserve">Jannatil Anwar Bin Jaharuddin </t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>01/14/2025</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>02/17/2025</t>
+          <t>01/28/2025</t>
         </is>
       </c>
       <c r="G13" s="3" t="n"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WBS004_UI - Logout Confirmation Screen </t>
+          <t xml:space="preserve">WBS001PRO002_CreateLogoutFunction </t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuramira Binti Ahmad Mahmud </t>
+          <t xml:space="preserve">Nur Ain Binti Mahamad Salleh </t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>01/13/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>01/15/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="G14" s="3" t="n"/>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WBS001PRO002_CreateLogoutFunction </t>
+          <t xml:space="preserve">WBS001PRO003_CreateRegisterFunction </t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>01/13/2025</t>
+          <t>01/14/2025</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>01/17/2025</t>
+          <t>01/28/2025</t>
         </is>
       </c>
       <c r="G15" s="3" t="n"/>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muhammad Izzun Mustaqim Bin Ismahdi </t>
+          <t xml:space="preserve">Jannatil Anwar Bin Jaharuddin </t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>01/20/2025</t>
+          <t>01/29/2025</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>01/24/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="G16" s="3" t="n"/>
@@ -2594,36 +2594,12 @@
       <c r="BM16" s="17" t="n"/>
     </row>
     <row r="17" ht="12.6" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 </t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code Review - WBS001PRO001_CreateLoginFunction </t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Muhammad Izzun Mustaqim Bin Ismahdi </t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To do </t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>01/29/2025</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>01/31/2025</t>
-        </is>
-      </c>
+      <c r="A17" s="20" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
@@ -2685,36 +2661,12 @@
       <c r="BM17" s="17" t="n"/>
     </row>
     <row r="18" ht="12.6" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10 </t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code Review - WBS001PRO003_CreateRegisterFunction </t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Muhammad Izzun Mustaqim Bin Ismahdi </t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To do </t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>02/19/2025</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>02/21/2025</t>
-        </is>
-      </c>
+      <c r="A18" s="20" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="n"/>
@@ -2776,36 +2728,12 @@
       <c r="BM18" s="17" t="n"/>
     </row>
     <row r="19" ht="12.6" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 </t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Testing - Login/Registration </t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nuramira Binti Ahmad Mahmud </t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To do </t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>01/29/2025</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>02/01/2025</t>
-        </is>
-      </c>
+      <c r="A19" s="20" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
@@ -2867,36 +2795,12 @@
       <c r="BM19" s="17" t="n"/>
     </row>
     <row r="20" ht="12.6" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 </t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Testing - Logout functionality </t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nur Ain Binti Mahamad Salleh </t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To do </t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>01/20/2025</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>01/22/2025</t>
-        </is>
-      </c>
+      <c r="A20" s="20" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
@@ -2958,36 +2862,12 @@
       <c r="BM20" s="17" t="n"/>
     </row>
     <row r="21" ht="12.6" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 </t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Integration Testing - UI and Backend </t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nur Ain Binti Mahamad Salleh &amp; Nuramira Binti Ahmad Mahmud  </t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To do </t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>02/03/2025</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>02/07/2025</t>
-        </is>
-      </c>
+      <c r="A21" s="20" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
@@ -3049,36 +2929,12 @@
       <c r="BM21" s="17" t="n"/>
     </row>
     <row r="22" ht="12.6" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14 </t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User Acceptance Testing (UAT) - All Features </t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">All Team Members </t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To do </t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>02/19/2025</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
-        </is>
-      </c>
+      <c r="A22" s="20" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
@@ -3140,36 +2996,12 @@
       <c r="BM22" s="17" t="n"/>
     </row>
     <row r="23" ht="12.6" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 </t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Final Code Review and Refinements </t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jaharuddin, Jannatil Anwar Bin </t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To do </t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>03/04/2025</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>03/10/2025</t>
-        </is>
-      </c>
+      <c r="A23" s="20" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
@@ -3231,36 +3063,12 @@
       <c r="BM23" s="17" t="n"/>
     </row>
     <row r="24" ht="12.6" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16 </t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deployment Preparation </t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jaharuddin, Jannatil Anwar Bin </t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To do </t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>03/11/2025</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>03/13/2025</t>
-        </is>
-      </c>
+      <c r="A24" s="20" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
